--- a/artfynd/A 59435-2024 artfynd.xlsx
+++ b/artfynd/A 59435-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126288469</v>
       </c>
       <c r="B2" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126288470</v>
       </c>
       <c r="B3" t="n">
-        <v>100500</v>
+        <v>100504</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126288468</v>
       </c>
       <c r="B4" t="n">
-        <v>105356</v>
+        <v>105369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59435-2024 artfynd.xlsx
+++ b/artfynd/A 59435-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126288469</v>
       </c>
       <c r="B2" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126288470</v>
       </c>
       <c r="B3" t="n">
-        <v>100504</v>
+        <v>100507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126288468</v>
       </c>
       <c r="B4" t="n">
-        <v>105369</v>
+        <v>105372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59435-2024 artfynd.xlsx
+++ b/artfynd/A 59435-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126288469</v>
       </c>
       <c r="B2" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>126288470</v>
       </c>
       <c r="B3" t="n">
-        <v>100507</v>
+        <v>100516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>126288468</v>
       </c>
       <c r="B4" t="n">
-        <v>105372</v>
+        <v>105381</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 59435-2024 artfynd.xlsx
+++ b/artfynd/A 59435-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126288469</v>
+        <v>126288470</v>
       </c>
       <c r="B2" t="n">
-        <v>105381</v>
+        <v>101299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221725</v>
+        <v>1365</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>764311</v>
+        <v>764308</v>
       </c>
       <c r="R2" t="n">
-        <v>7354116</v>
+        <v>7354123</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126288470</v>
+        <v>126288468</v>
       </c>
       <c r="B3" t="n">
-        <v>100516</v>
+        <v>106229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1365</v>
+        <v>221725</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>764308</v>
+        <v>764300</v>
       </c>
       <c r="R3" t="n">
-        <v>7354123</v>
+        <v>7354116</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126288468</v>
+        <v>126288469</v>
       </c>
       <c r="B4" t="n">
-        <v>105381</v>
+        <v>106229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>764300</v>
+        <v>764311</v>
       </c>
       <c r="R4" t="n">
         <v>7354116</v>

--- a/artfynd/A 59435-2024 artfynd.xlsx
+++ b/artfynd/A 59435-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288470</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288468</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126288469</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>